--- a/data/dados_brutos.xlsx
+++ b/data/dados_brutos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaike\OneDrive\Documentos\GitHub\analise-vendas-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1EBDC5-D576-4F6B-A61F-207B1727A330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD9BE3-4876-498C-9046-A929A9EC279F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
